--- a/www/download/COUNTRY.NOR.zdW16.xlsx
+++ b/www/download/COUNTRY.NOR.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Noruega</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>8.78076126254857</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>8.98798496076842</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>7.93210388256787</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>7.11102225356316</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>6.73424523280679</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>6.43998439742794</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>6.40702430779204</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>5.84593774822521</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>5.5627108511722</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>6.25434354345176</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>6.03727045673454</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>5.60001536334162</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>5.81412112880623</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>5.86964759545451</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.28032036825306</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.328</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.343</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.318</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.331</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.362</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.442</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.542</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.626</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.612</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.601</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.638</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.689</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.727</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.747</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.155</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.159</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.171</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.144</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.156</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.193</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.374</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.464</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.443</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.442</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.476</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.526</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.562</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.588</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3293.21</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3249.445</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3223.564</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3165.899</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3229.615</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3280.768</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3384.942</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3549.279</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3672.623</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3618.799</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3612.94</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3685.378</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3751.593</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3785.21</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>3830.627</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3937315903.43706</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3853113625.72378</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3863614681.44266</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3919251149.50189</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4068188090.45955</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>4129990466.87408</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>4170392080.31901</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>4518298903.14897</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>4520307048.35747</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4040407285.70311</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>4041686136.56444</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>4308305035.1152</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>4368778697.93788</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>4461428439.40002</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>4421228146.20493</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2330374910.32266</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2471799824.57533</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2595262062.55103</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2646375242.59014</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2893750567.54376</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2872116573.09089</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3003212809.95938</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3168251625.54171</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3202180208.36056</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3049455571.45788</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2768171939.55112</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3094438852.94785</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2884791728.05203</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3233550536.47227</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3286094748.10312</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>954214.489052793</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>891642.222435667</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>785867.364325922</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>716385.530813816</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>648798.328709281</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>576399.334244706</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>500074.039401775</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>438274.176466744</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>385416.410122252</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>393280.367351092</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>361582.649515035</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>338708.400980928</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>339250.877154915</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>332709.160157269</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>327884.502554152</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>16434.624861929</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15952.4399087117</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16065.1181588246</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>17297.0793704886</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>19384.6748270055</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21262.6115106894</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>23174.092427173</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>27218.7391539167</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>30593.2201575276</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>27554.4566394261</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>30378.7557957818</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>33037.1740732228</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>32891.9296982112</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>33174.1547151973</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>33694.4664302029</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>35716.7304175996</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>34441.0973102351</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>34788.9906545393</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>38420.1902567357</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>43948.8044469382</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>48189.4937913885</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>51420.5575055618</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>62493.9464302253</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>68190.0621745581</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>55702.5258914399</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>61561.1144552607</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>69967.8205558838</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>69304.9525095081</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>70364.3427758508</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>69973.746576493</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.306656704254681</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.215713331687883</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.150943499348929</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.105663306136503</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0332611364420168</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0615864371823698</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0495426729491852</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.0488434609204462</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.0792646806624895</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.111345917520548</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.227886155276603</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.120396997567825</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.224005173636684</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.101575484849561</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.0997856961020864</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.78076126254857</t>
+          <t>1081.38046882722</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.98798496076842</t>
+          <t>1144.88180851104</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.93210388256787</t>
+          <t>1195.42241480932</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7.11102225356316</t>
+          <t>1234.31681090958</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6.73424523280679</t>
+          <t>1342.18486435239</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6.43998439742794</t>
+          <t>1309.67467993201</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>6.40702430779204</t>
+          <t>1323.00123786757</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.84593774822521</t>
+          <t>1334.56260553568</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.5627108511722</t>
+          <t>1299.58612352295</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6.25434354345176</t>
+          <t>1248.24214959389</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6.03727045673454</t>
+          <t>1133.56754281373</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>5.60001536334162</t>
+          <t>1249.77336548782</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>5.81412112880623</t>
+          <t>1142.03948062234</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5.86964759545451</t>
+          <t>1262.119647335</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6.28032036825306</t>
+          <t>1269.74294748961</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>6552802722.6929</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>6784878600.73355</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>6589491389.66067</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>7065232001.47104</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>7872985472.92086</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>9253448934.24355</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>9806286145.67062</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>8688323993.2874</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>10110159702.3017</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>7305120833.60971</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>7144266238.33809</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>8529618781.88975</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>8441602245.1636</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>8205721545.13451</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>7419367171.14506</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>7365573627.59964</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>7671999543.62508</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>7606862846.64526</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>8145063720.46516</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>8971423320.27027</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>10337786539.2685</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>10824149370.8678</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>9820786148.56301</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>11231758326.7428</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>8476899275.11232</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>8444790272.63023</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>9897104757.64014</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>9935529112.89061</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>9689519399.58123</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>8772608644.0215</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>-812770904.906735</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-887120942.891522</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>-1017371456.9846</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1079831718.99412</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>-1098437847.34941</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>-1084337605.02498</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>-1017863225.19717</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1132462155.27562</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1121598624.44109</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>-1171778441.5026</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.201</t>
+          <t>-1300524034.29214</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>-1367485975.75039</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>-1493926867.72701</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>-1483797854.44672</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>-1353241472.87645</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>1412.99303944316</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>1391.8480778138</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>1375.86365730078</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1364.73880597015</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>1386.82745825603</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>1390.33287733698</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1388.54625550661</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>1399.74726200505</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>1402.5974025974</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>1387.22881702824</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>1391.89189189189</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>1400.24232633279</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1397.8622327791</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>1390.32006245121</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>1396.44513137558</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1414.60912399271</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1394.61153874586</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>1375.82754217891</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>1365.78917259076</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1385.50613662572</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1388.97889818795</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>1386.13519163017</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>1396.25462510069</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>1398.56175010179</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>1385.45135194252</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>1389.05817665983</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>1397.03478356536</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>1395.16283188987</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>1388.04917414791</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>1394.47658196423</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>76169.7407171746</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>75982.8308532573</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76837.4625463018</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>87363.1473215578</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>105255.951300737</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>130306.621332898</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>150426.384193555</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>169165.586702119</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>210208.385749881</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>147785.150910255</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>165868.432580254</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>200182.394155131</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>201658.65403179</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>199376.008242583</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>188130.64991241</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1027696874.79474</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1004115040.92066</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>954499711.02214</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>970804410.502459</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>984578997.275406</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>997062739.268823</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1009194666.98263</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1095024017.40958</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1104049051.55194</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>968091217.515701</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>987557695.455961</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1058192522.07209</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1042944324.38971</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1054177630.64789</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1011852497.92706</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>43577.9185603864</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>43433.8796681205</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>46897.5960105832</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>53288.3863007638</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>63734.7799524282</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>72892.5624622443</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>82617.8361641521</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>104246.627704892</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>117668.629917428</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>93370.7834897156</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>106056.366296212</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>122591.025920289</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>121378.240980899</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>127473.92008699</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>125767.145872063</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3293.21</t>
+          <t>3123408551.06847</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3249.445</t>
+          <t>3156272945.97018</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3223.564</t>
+          <t>3255747804.12758</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3165.899</t>
+          <t>3435610872.73625</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3229.615</t>
+          <t>3749470613.52548</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3280.768</t>
+          <t>3844298737.15567</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3384.942</t>
+          <t>3948926811.70713</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3549.279</t>
+          <t>4146341430.07748</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3672.623</t>
+          <t>4198880852.50101</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3618.799</t>
+          <t>3639735564.11207</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3612.94</t>
+          <t>3591639282.2834</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3685.378</t>
+          <t>4012035481.38156</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3751.593</t>
+          <t>3677102303.61352</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>3785.21</t>
+          <t>4006678275.81016</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3830.627</t>
+          <t>3918654555.10912</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>32591.8221567882</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>32548.9511851368</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>29939.8665357186</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>34074.761020794</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>41521.1713483092</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>57414.0588706536</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>67808.5480294033</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>64918.9589972264</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>92539.7558324529</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>54414.3674205399</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>59812.0662840424</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>77591.3682348417</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>80280.4130508915</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>71902.0881555937</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>62363.5040403465</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4977.193</t>
+          <t>-2095711676.27372</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4777.318</t>
+          <t>-2152157905.04953</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4781.985</t>
+          <t>-2301248093.10544</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4878.519</t>
+          <t>-2464806462.23379</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4950.69</t>
+          <t>-2764891616.25008</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5109.623</t>
+          <t>-2847235997.88685</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5146.068</t>
+          <t>-2939732144.7245</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>5506.037</t>
+          <t>-3051317412.66789</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5614.162</t>
+          <t>-3094831800.94907</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5107.29</t>
+          <t>-2671644346.59637</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>5090.553</t>
+          <t>-2604081586.82744</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>5522.959</t>
+          <t>-2953842959.30947</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>5429.506</t>
+          <t>-2634157979.22381</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>5559.204</t>
+          <t>-2952500645.16227</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>4421.228</t>
+          <t>-2906802057.18206</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>92424.951764</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>92471.19002</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>101459.41938</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>117854.285501</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>139672.516176</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>170088.58776</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>194491.293048</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>216227.57548</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>265273.75036</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>204186.24745</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>227555.42334</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>272728.5513</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>276890.684532</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>281556.238994</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>266179.601988253</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1811.709</t>
+          <t>0.168236759000517</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1784.687</t>
+          <t>0.161564350861885</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1784.169</t>
+          <t>0.148446918624336</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1764.478</t>
+          <t>0.152784331245575</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1794.372</t>
+          <t>0.16628849268129</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1822.272</t>
+          <t>0.182511232707263</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1879.502</t>
+          <t>0.189431113458133</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1967.909</t>
+          <t>0.171287832112446</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2028.019</t>
+          <t>0.181677751116931</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1998.675</t>
+          <t>0.14070900147628</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1994.464</t>
+          <t>0.149815493546752</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2034.281</t>
+          <t>0.154747210643744</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2073.41</t>
+          <t>0.154995114107908</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2103.397</t>
+          <t>0.147984262569206</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2128.955</t>
+          <t>0.140024678301895</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>72915.5501116402</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>75586.0398794097</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>89641.5211579208</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>102854.018838523</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>113942.755610106</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>126651.961675891</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>139105.301433405</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>169560.483458525</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>196014.3627115</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>179520.170709978</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>191247.804084582</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>219225.33161615</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>225328.677503809</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>236163.18151627</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>230440.226408123</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2741.309</t>
+          <t>78028.3749192772</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2859.475</t>
+          <t>80985.9328967418</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3000.298</t>
+          <t>95922.756360814</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3066.857</t>
+          <t>110170.981708347</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3298.455</t>
+          <t>122025.243507881</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3304.827</t>
+          <t>135312.393482932</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3450.037</t>
+          <t>148591.566544745</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3610.65</t>
+          <t>180305.322098969</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3688.957</t>
+          <t>207195.93247822</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3548.203</t>
+          <t>190419.32413751</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>3223.105</t>
+          <t>202069.863592381</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>3616.979</t>
+          <t>231570.19161041</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>3360.782</t>
+          <t>237890.404897611</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>3735.256</t>
+          <t>249440.376640236</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3286.095</t>
+          <t>243143.963322222</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>436115.207490924</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>450358.784317831</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>522856.905898737</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>599820.983801101</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>679159.523636757</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>768291.74424481</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>844000.213257616</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>1029605.06014961</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>1179640.13277467</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1110706.35252739</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>1201226.02613738</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>1384901.39606438</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>1413383.49397177</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>1479257.9756484</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>1471086.95179907</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>122169.822456739</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>126365.9068654</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>133602.841229854</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>131287.15287377</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>132332.015923228</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>129312.944044329</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>134355.562201427</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>134950.280454151</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>139960.688609969</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>140856.811592655</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>138933.554819263</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>143017.456271887</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>148007.130278909</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>151825.356478706</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>154602.515505014</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>115412.221507146</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>119266.135750643</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>123941.154294431</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>121226.811178632</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>122888.543747242</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>120616.218596994</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>125533.508735255</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>126789.385929236</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>132203.308307374</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>132729.424595369</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>131492.828793296</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>135281.507172334</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>139835.535759226</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>143511.704127461</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>146392.751675172</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>73370.6090591112</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>72761.9246432582</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77616.496562122</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>91643.2478771143</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>112936.413475699</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>140221.873320934</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>159879.900156292</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>176358.818685031</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>214314.36644978</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>156286.38179749</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>179962.269966975</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>214309.62805759</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>219067.535926389</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>218906.900675945</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>205988.47717978</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.045e+09</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3.005e+09</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2.987e+09</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2.926e+09</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2.99e+09</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3.049e+09</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3.152e+09</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3.323e+09</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3.456e+09</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3.389e+09</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3.399e+09</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3.467e+09</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3.531e+09</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3.562e+09</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>3.614e+09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3293210040.65503</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3249444885.27786</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3223563931.32518</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3165899302.06539</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3229614804.47456</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3280768157.51993</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3384942137.96087</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3549279257.00595</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3672623155.76729</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3618798931.27386</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3612940317.49222</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3685377759.04541</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3751592854.95187</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3785210097.90135</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3830627170.65573</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1811708660.88038</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1784686562.74579</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1784168646.7396</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1764478461.78814</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1794371980.33151</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1822272365.42764</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1879502211.08376</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1967908994.21834</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2028019102.78388</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1998674666.50442</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1994463505.61309</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2034281220.6357</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2073409714.54964</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2103396570.77324</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2128954509.95639</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2328000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2330000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2343000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2318000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2331000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2362000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2442000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2542000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2626000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2612000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2601000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2638000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2689000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2727000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2747000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2155000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2159000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2171000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2144000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2156000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2193000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2270000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2374000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2464000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2443000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2442000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2476000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2526000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2562000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2588000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3293210040.65503</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3249444885.27786</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3223563931.32518</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3165899302.06539</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3229614804.47456</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3280768157.51993</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3384942137.96087</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3549279257.00595</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3672623155.76729</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3618798931.27386</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3612940317.49222</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3685377759.04541</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3751592854.95187</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3785210097.90135</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3830627170.65573</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3.045e+09</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3.005e+09</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2.987e+09</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2.926e+09</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2.99e+09</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3.049e+09</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3.152e+09</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3.323e+09</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3.456e+09</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3.389e+09</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3.399e+09</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3.467e+09</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>3.531e+09</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>3.562e+09</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>3.614e+09</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>277219.052132</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>283967.45162</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>322105.353592</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>371147.840972</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>427152.010912</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>495268.35504</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>559533.699036</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>668111.836196</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>779494.002248</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>646524.762065</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>700849.568606</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>815806.182</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>832712.786136</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>858418.687865</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>835078.908764</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>151398.756208</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>153747.9688</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>173539.126849</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>201814.088954</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>234961.359904</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>275533.95624</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>308471.77881</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>356664.311842</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>421510.298928</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>346705.705935</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>382032.299191</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>445879.819668</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>456957.940824</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>468347.447642</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>449132.121946</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>645293.601595254</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>666819.228126666</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>683279.112393686</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>673612.673530537</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>684205.847749086</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>691311.584113677</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>709383.478048119</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>768727.172676689</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>768619.88900034</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>830538.085057171</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>825905.510198592</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>839735.63395038</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>868921.796301258</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>893146.909582215</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>937498.933330622</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
